--- a/Actuator test/Accuracy actuator 8DOF cell stretcher.xlsx
+++ b/Actuator test/Accuracy actuator 8DOF cell stretcher.xlsx
@@ -1,24 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ferrerx\Documents\GitHub\Cell_stretcher_8DOF\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ferrerx\Documents\GitHub\Cell_stretcher_8DOF\Actuator test\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43F2AF8F-863C-4C35-A644-1770B40289E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="21943" windowHeight="8511"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet3" sheetId="3" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="4" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -42,14 +53,18 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="12">
@@ -132,9 +147,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -143,10 +167,10 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -158,15 +182,7 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -224,7 +240,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -596,7 +611,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -719,7 +733,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -889,7 +902,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1513,7 +1525,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
@@ -1594,7 +1605,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
@@ -2978,7 +2988,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -3013,7 +3029,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4" name="Chart 3"/>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -3043,7 +3065,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="14" name="Chart 13"/>
+        <xdr:cNvPr id="14" name="Chart 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr>
           <a:graphicFrameLocks/>
         </xdr:cNvGraphicFramePr>
@@ -3325,11 +3353,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="E6:J33"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="6" spans="5:10" x14ac:dyDescent="0.4">
+    <row r="6" spans="5:10" x14ac:dyDescent="0.3">
       <c r="E6" t="s">
         <v>0</v>
       </c>
@@ -3337,7 +3365,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="5:10" x14ac:dyDescent="0.4">
+    <row r="7" spans="5:10" x14ac:dyDescent="0.3">
       <c r="E7">
         <v>0</v>
       </c>
@@ -3345,7 +3373,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="5:10" x14ac:dyDescent="0.4">
+    <row r="8" spans="5:10" x14ac:dyDescent="0.3">
       <c r="E8">
         <v>10</v>
       </c>
@@ -3364,7 +3392,7 @@
         <v>15.884615384615385</v>
       </c>
     </row>
-    <row r="9" spans="5:10" x14ac:dyDescent="0.4">
+    <row r="9" spans="5:10" x14ac:dyDescent="0.3">
       <c r="E9">
         <v>20</v>
       </c>
@@ -3376,7 +3404,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="5:10" x14ac:dyDescent="0.4">
+    <row r="10" spans="5:10" x14ac:dyDescent="0.3">
       <c r="E10">
         <v>30</v>
       </c>
@@ -3388,7 +3416,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="5:10" x14ac:dyDescent="0.4">
+    <row r="11" spans="5:10" x14ac:dyDescent="0.3">
       <c r="E11">
         <v>40</v>
       </c>
@@ -3400,7 +3428,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="5:10" x14ac:dyDescent="0.4">
+    <row r="12" spans="5:10" x14ac:dyDescent="0.3">
       <c r="E12">
         <v>50</v>
       </c>
@@ -3412,7 +3440,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="5:10" x14ac:dyDescent="0.4">
+    <row r="13" spans="5:10" x14ac:dyDescent="0.3">
       <c r="E13">
         <v>60</v>
       </c>
@@ -3424,7 +3452,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="5:10" x14ac:dyDescent="0.4">
+    <row r="14" spans="5:10" x14ac:dyDescent="0.3">
       <c r="E14">
         <v>70</v>
       </c>
@@ -3436,7 +3464,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="5:10" x14ac:dyDescent="0.4">
+    <row r="15" spans="5:10" x14ac:dyDescent="0.3">
       <c r="E15">
         <v>80</v>
       </c>
@@ -3448,7 +3476,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="5:10" x14ac:dyDescent="0.4">
+    <row r="16" spans="5:10" x14ac:dyDescent="0.3">
       <c r="E16">
         <v>90</v>
       </c>
@@ -3460,7 +3488,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="5:7" x14ac:dyDescent="0.4">
+    <row r="17" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E17">
         <v>100</v>
       </c>
@@ -3472,7 +3500,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="5:7" x14ac:dyDescent="0.4">
+    <row r="18" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E18">
         <v>110</v>
       </c>
@@ -3484,7 +3512,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="5:7" x14ac:dyDescent="0.4">
+    <row r="19" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E19">
         <v>120</v>
       </c>
@@ -3496,7 +3524,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="5:7" x14ac:dyDescent="0.4">
+    <row r="20" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E20">
         <v>130</v>
       </c>
@@ -3508,7 +3536,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="5:7" x14ac:dyDescent="0.4">
+    <row r="21" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E21">
         <v>140</v>
       </c>
@@ -3520,7 +3548,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="5:7" x14ac:dyDescent="0.4">
+    <row r="22" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E22">
         <v>150</v>
       </c>
@@ -3532,7 +3560,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="5:7" x14ac:dyDescent="0.4">
+    <row r="23" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E23">
         <v>160</v>
       </c>
@@ -3544,7 +3572,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="5:7" x14ac:dyDescent="0.4">
+    <row r="24" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E24">
         <v>170</v>
       </c>
@@ -3556,7 +3584,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="5:7" x14ac:dyDescent="0.4">
+    <row r="25" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E25">
         <v>180</v>
       </c>
@@ -3568,7 +3596,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="26" spans="5:7" x14ac:dyDescent="0.4">
+    <row r="26" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E26">
         <v>190</v>
       </c>
@@ -3580,7 +3608,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="5:7" x14ac:dyDescent="0.4">
+    <row r="27" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E27">
         <v>200</v>
       </c>
@@ -3592,7 +3620,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="5:7" x14ac:dyDescent="0.4">
+    <row r="28" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E28">
         <v>210</v>
       </c>
@@ -3604,7 +3632,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="29" spans="5:7" x14ac:dyDescent="0.4">
+    <row r="29" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E29">
         <v>220</v>
       </c>
@@ -3616,7 +3644,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="5:7" x14ac:dyDescent="0.4">
+    <row r="30" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E30">
         <v>230</v>
       </c>
@@ -3628,7 +3656,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="5:7" x14ac:dyDescent="0.4">
+    <row r="31" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E31">
         <v>240</v>
       </c>
@@ -3640,7 +3668,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="32" spans="5:7" x14ac:dyDescent="0.4">
+    <row r="32" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E32">
         <v>250</v>
       </c>
@@ -3652,7 +3680,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="33" spans="5:7" x14ac:dyDescent="0.4">
+    <row r="33" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E33">
         <v>260</v>
       </c>
@@ -3671,11 +3699,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A5:V16"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -3699,49 +3727,49 @@
       <c r="S5" s="1"/>
       <c r="T5" s="1"/>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.4">
-      <c r="A6" s="3">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A6" s="6">
         <v>1</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="5">
+      <c r="B6" s="6"/>
+      <c r="C6" s="7">
         <v>2</v>
       </c>
-      <c r="D6" s="5"/>
-      <c r="E6" s="4">
+      <c r="D6" s="7"/>
+      <c r="E6" s="8">
         <v>3</v>
       </c>
-      <c r="F6" s="4"/>
-      <c r="G6" s="6">
+      <c r="F6" s="8"/>
+      <c r="G6" s="9">
         <v>4</v>
       </c>
-      <c r="H6" s="6"/>
-      <c r="I6" s="7">
+      <c r="H6" s="9"/>
+      <c r="I6" s="10">
         <v>5</v>
       </c>
-      <c r="J6" s="7"/>
-      <c r="K6" s="8">
+      <c r="J6" s="10"/>
+      <c r="K6" s="11">
         <v>6</v>
       </c>
-      <c r="L6" s="8"/>
-      <c r="M6" s="9">
+      <c r="L6" s="11"/>
+      <c r="M6" s="2">
         <v>7</v>
       </c>
-      <c r="N6" s="9"/>
-      <c r="O6" s="10">
+      <c r="N6" s="2"/>
+      <c r="O6" s="3">
         <v>8</v>
       </c>
-      <c r="P6" s="10"/>
-      <c r="Q6" s="11">
+      <c r="P6" s="3"/>
+      <c r="Q6" s="4">
         <v>9</v>
       </c>
-      <c r="R6" s="11"/>
-      <c r="S6" s="2">
+      <c r="R6" s="4"/>
+      <c r="S6" s="5">
         <v>10</v>
       </c>
-      <c r="T6" s="2"/>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="T6" s="5"/>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>316</v>
       </c>
@@ -3803,7 +3831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>941</v>
       </c>
@@ -3875,7 +3903,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>1574</v>
       </c>
@@ -3947,7 +3975,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2209</v>
       </c>
@@ -4019,7 +4047,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
       <c r="C13" s="1">
         <v>1</v>
       </c>
@@ -4061,7 +4089,7 @@
       </c>
       <c r="V13" s="1"/>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
       <c r="C14">
         <v>400</v>
       </c>
@@ -4133,7 +4161,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
       <c r="C15">
         <v>800</v>
       </c>
@@ -4205,7 +4233,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
       <c r="C16">
         <v>1200</v>
       </c>
@@ -4279,29 +4307,149 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="O13:P13"/>
-    <mergeCell ref="Q13:R13"/>
-    <mergeCell ref="S13:T13"/>
-    <mergeCell ref="U13:V13"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="K13:L13"/>
     <mergeCell ref="M6:N6"/>
     <mergeCell ref="O6:P6"/>
     <mergeCell ref="Q6:R6"/>
     <mergeCell ref="S6:T6"/>
     <mergeCell ref="A5:T5"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="K13:L13"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="E6:F6"/>
     <mergeCell ref="G6:H6"/>
     <mergeCell ref="I6:J6"/>
     <mergeCell ref="K6:L6"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="O13:P13"/>
+    <mergeCell ref="Q13:R13"/>
+    <mergeCell ref="S13:T13"/>
+    <mergeCell ref="U13:V13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C2D2523-C342-434D-85A1-D6279D97CCC5}">
+  <dimension ref="C4:E13"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="4" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C4" s="12">
+        <v>625</v>
+      </c>
+      <c r="D4" s="12">
+        <v>1258</v>
+      </c>
+      <c r="E4" s="12">
+        <v>1893</v>
+      </c>
+    </row>
+    <row r="5" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C5" s="12">
+        <v>627</v>
+      </c>
+      <c r="D5" s="12">
+        <v>1260</v>
+      </c>
+      <c r="E5" s="12">
+        <v>1895</v>
+      </c>
+    </row>
+    <row r="6" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C6" s="12">
+        <v>628</v>
+      </c>
+      <c r="D6" s="12">
+        <v>1264</v>
+      </c>
+      <c r="E6" s="12">
+        <v>1899</v>
+      </c>
+    </row>
+    <row r="7" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C7" s="12">
+        <v>628</v>
+      </c>
+      <c r="D7" s="12">
+        <v>1263</v>
+      </c>
+      <c r="E7" s="12">
+        <v>1899</v>
+      </c>
+    </row>
+    <row r="8" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C8" s="12">
+        <v>631</v>
+      </c>
+      <c r="D8" s="12">
+        <v>1266</v>
+      </c>
+      <c r="E8" s="12">
+        <v>1901</v>
+      </c>
+    </row>
+    <row r="9" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C9" s="12">
+        <v>631</v>
+      </c>
+      <c r="D9" s="12">
+        <v>1266</v>
+      </c>
+      <c r="E9" s="12">
+        <v>1901</v>
+      </c>
+    </row>
+    <row r="10" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C10" s="12">
+        <v>631</v>
+      </c>
+      <c r="D10" s="12">
+        <v>1266</v>
+      </c>
+      <c r="E10" s="12">
+        <v>1902</v>
+      </c>
+    </row>
+    <row r="11" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C11" s="12">
+        <v>631</v>
+      </c>
+      <c r="D11" s="12">
+        <v>1267</v>
+      </c>
+      <c r="E11" s="12">
+        <v>1902</v>
+      </c>
+    </row>
+    <row r="12" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C12" s="12">
+        <v>631</v>
+      </c>
+      <c r="D12" s="12">
+        <v>1266</v>
+      </c>
+      <c r="E12" s="12">
+        <v>1902</v>
+      </c>
+    </row>
+    <row r="13" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C13" s="12">
+        <v>632</v>
+      </c>
+      <c r="D13" s="12">
+        <v>1267</v>
+      </c>
+      <c r="E13" s="12">
+        <v>1902</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>